--- a/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
+++ b/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/07 15:06:11</t>
+          <t>10/18 20:18:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>198267.27</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26087.8</t>
+          <t>1651.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,237 +117,279 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/07 15:06:11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>198267.27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26087.8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/03 13:14:57</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>325000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>39393.94</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/07 20:03:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/07 20:03:45</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>26087</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/03 15:01:38</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>39393</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>523267.27</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>65481.74</t>
+          <t>541264.27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>65480</t>
+          <t>67132.84</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.74</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1652.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
+++ b/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/07 20:03:45</t>
+          <t>10/18 21:36:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/07 20:03:45</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26087</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/03 15:01:38</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>39393</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>541264.27</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>67132.84</t>
+          <t>541264.27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>65480</t>
+          <t>67132.84</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>67131</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1652.84</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
+++ b/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 20:18:16</t>
+          <t>10/31 11:20:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1651.1</t>
+          <t>18552.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/07 15:06:11</t>
+          <t>10/18 20:18:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>198267.27</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26087.8</t>
+          <t>1651.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,166 +159,181 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09/07 15:06:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>198267.27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26087.8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/03 13:14:57</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>325000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>39393.94</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/18 21:36:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/07 20:03:45</t>
+          <t>10/31 11:20:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -340,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/03 15:01:38</t>
+          <t>10/18 21:36:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>39393</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -364,59 +379,113 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>09/07 20:03:45</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26087</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>541264.27</t>
-        </is>
-      </c>
-    </row>
+          <t>07/03 15:01:38</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>39393</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>67132.84</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>698964.27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>85685.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>68131</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1.84</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17554.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
+++ b/bills/JXZFSP01/-5226485600/7311f8a2942c1fa04aad14e4019fc05baaeec57e8dc1031a16b5a843a2c4ed63/bill-all.xlsx
@@ -328,12 +328,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/31 11:20:31</t>
+          <t>10/31 15:02:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -355,12 +355,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/18 21:36:40</t>
+          <t>10/31 11:20:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -382,12 +382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/07 20:03:45</t>
+          <t>10/18 21:36:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -409,83 +409,110 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>09/07 20:03:45</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26087</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/03 15:01:38</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>39393</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>698964.27</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>85685.78</t>
+          <t>698964.27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>68131</t>
+          <t>85685.78</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>85683</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>17554.78</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.78</t>
         </is>
       </c>
     </row>
